--- a/procurement/PR-01_initial_request.xlsx
+++ b/procurement/PR-01_initial_request.xlsx
@@ -1817,7 +1817,7 @@
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rule: ID ≥ 1/2 in (12.7 mm), cross-section ≤ 1/8 in (3.18 mm) (§3.1.3).</t>
+          <t xml:space="preserve">Rule: ID ≥ 1/2 in (12.7 mm), cross-section ≤ 1/8 in (3.175 mm) (§3.1.3).</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-02, TC-04, SR-10</t>
+          <t xml:space="preserve">TC-02, TC-04, SR-12</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-04, SR-04, SR-12</t>
+          <t xml:space="preserve">TC-04, SR-04, SR-15</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">

--- a/procurement/PR-01_initial_request.xlsx
+++ b/procurement/PR-01_initial_request.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Read me" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Items!$A$1:$U$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Items!$A$1:$U$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Items!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -174,7 +174,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U75"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="43.5" customHeight="1">
+    <row r="41" ht="84" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">B07</t>
@@ -4036,19 +4036,19 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor candidates</t>
+          <t xml:space="preserve">Motors: bench pair (both D9 candidates)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushless outrunner; class set by Scripts 3–4 at the 13 Oct gate. Reference: T-Motor AT4130 long shaft (230/300/450 KV, 6–12S).</t>
+          <t xml:space="preserve">T-Motor AT7215 30CC fixed-wing motor: 1 x KV270 (8S candidate) and 1 x KV200 (12S candidate), the two leads of the propulsion study (analysis/out/prop_trade_report.txt). Both are bench-tested (TC-06) before D9; the flight motors are B07b.</t>
         </is>
       </c>
       <c r="F41" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="15">
-        <v>119.9</v>
+        <v>219.0</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -4057,23 +4057,23 @@
       </c>
       <c r="I41" s="5">
         <f>G41</f>
-        <v>119.9</v>
+        <v>219.0</v>
       </c>
       <c r="J41" s="5">
         <f>F41*I41</f>
-        <v>359.7</v>
+        <v>438.0</v>
       </c>
       <c r="K41" s="6">
         <f>I41*'Read me'!$B$4</f>
-        <v>37.2684</v>
+        <v>68.0716</v>
       </c>
       <c r="L41" s="6">
         <f>F41*K41</f>
-        <v>111.8052</v>
+        <v>136.1431</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget hold</t>
+          <t xml:space="preserve">Buy now</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4083,17 +4083,17 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-Motor</t>
+          <t xml:space="preserve">T-Motor (product price, all windings)</t>
         </is>
       </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://shop.tmotor.com/products/at4130-long-shaft</t>
+          <t xml:space="preserve">https://store.tmotor.com/product/at7215-fixed-wing-motor.html</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -4103,24 +4103,24 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.1, Scripts 3–4</t>
+          <t xml:space="preserve">§3.2.1, TC-06, DB-01 D9</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unmodified commercial motor (§3.2.1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="43.5" customHeight="1">
+          <t xml:space="preserve">Unmodified commercial motor (§3.2.1). KV270: 606 g with wires (T-Motor spec table).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B08</t>
+          <t xml:space="preserve">B07b</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4135,19 +4135,19 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESC candidates</t>
+          <t xml:space="preserve">Motors: flight and spare (after D9)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80–100 A, matched to B07; BEC disabled. Reference: Castle Phoenix Edge Lite 100 (2–8S, 100 A).</t>
+          <t xml:space="preserve">The winding chosen at D9 (KV270 for 8S or KV200 for 12S): one flight motor and one spare.</t>
         </is>
       </c>
       <c r="F42" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="15">
-        <v>149.95</v>
+        <v>219.0</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -4156,19 +4156,19 @@
       </c>
       <c r="I42" s="5">
         <f>G42</f>
-        <v>149.95</v>
+        <v>219.0</v>
       </c>
       <c r="J42" s="5">
         <f>F42*I42</f>
-        <v>449.85</v>
+        <v>438.0</v>
       </c>
       <c r="K42" s="6">
         <f>I42*'Read me'!$B$4</f>
-        <v>46.6088</v>
+        <v>68.0716</v>
       </c>
       <c r="L42" s="6">
         <f>F42*K42</f>
-        <v>139.8264</v>
+        <v>136.1431</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4182,17 +4182,17 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gator RC</t>
+          <t xml:space="preserve">T-Motor (product price, all windings)</t>
         </is>
       </c>
       <c r="P42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.gator-rc.com/products/castle-creations-phoenix-edge-lite-100-esc-with-built-in-5-amp-bec</t>
+          <t xml:space="preserve">https://store.tmotor.com/product/at7215-fixed-wing-motor.html</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -4207,19 +4207,19 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.3, FAQ A.3</t>
+          <t xml:space="preserve">§3.2.1, DB-01 D9</t>
         </is>
       </c>
       <c r="U42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+          <t xml:space="preserve">Unmodified commercial motor (§3.2.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="70.5" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B09</t>
+          <t xml:space="preserve">B08</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -4234,19 +4234,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Propellers and spares</t>
+          <t xml:space="preserve">ESC, fits both candidates</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">APC Electric (E) series; diameter and pitch from Script 3. Reference: APC 15×10E.</t>
+          <t xml:space="preserve">Castle Creations Phoenix Edge HV 120 (010-0104-00): 3S–12S LiPo, 120 A continuous at full throttle, no internal BEC, data logging (current, voltage, RPM); 148.8 g with wires. Bench, flight and spare.</t>
         </is>
       </c>
       <c r="F43" s="4">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G43" s="15">
-        <v>7.65</v>
+        <v>289.95</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -4255,23 +4255,23 @@
       </c>
       <c r="I43" s="5">
         <f>G43</f>
-        <v>7.65</v>
+        <v>289.95</v>
       </c>
       <c r="J43" s="5">
         <f>F43*I43</f>
-        <v>122.4</v>
+        <v>869.85</v>
       </c>
       <c r="K43" s="6">
         <f>I43*'Read me'!$B$4</f>
-        <v>2.3778</v>
+        <v>90.1249</v>
       </c>
       <c r="L43" s="6">
         <f>F43*K43</f>
-        <v>38.0455</v>
+        <v>270.3746</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget hold</t>
+          <t xml:space="preserve">Buy now</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4281,44 +4281,44 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gator RC</t>
+          <t xml:space="preserve">Castle Creations</t>
         </is>
       </c>
       <c r="P43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.gator-rc.com/products/15x10e-propeller-electric-apc</t>
+          <t xml:space="preserve">https://castlecreations.com/products/air-esc-phoenix-edge-120-hv-010-0104-00</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search result</t>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.1</t>
+          <t xml:space="preserve">§3.2.1, §4.2.5, TC-06, flight power logs (evidence E04)</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commercial propellers only; tips may be clipped (§3.2.1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="70.5" customHeight="1">
+          <t xml:space="preserve">Works on 8S and 12S, so buying it does not pre-empt D9. No BEC: the receiver runs on its own pack (B05). Programming and log download need a Castle Link USB adapter (not listed here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="57" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B10</t>
+          <t xml:space="preserve">B09</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -4333,19 +4333,19 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Propulsion LiPo packs</t>
+          <t xml:space="preserve">Propellers: bench sweep and spares</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">≤ 100 Wh per pack and in total on the airplane. Reference: Tattu R-Line 6S 4500 mAh 95C, 99.9 Wh, XT90-S, 10 AWG leads.</t>
+          <t xml:space="preserve">APC Thin Electric, from the propulsion study: 6 x 20x15E (lead), 2 x 20x13E, 2 x 20.5x14E, all US$18.20; the 21x13E is B09b.</t>
         </is>
       </c>
       <c r="F44" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G44" s="15">
-        <v>147.0</v>
+        <v>18.2</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -4354,23 +4354,23 @@
       </c>
       <c r="I44" s="5">
         <f>G44</f>
-        <v>147.0</v>
+        <v>18.2</v>
       </c>
       <c r="J44" s="5">
         <f>F44*I44</f>
-        <v>588.0</v>
+        <v>182.0</v>
       </c>
       <c r="K44" s="6">
         <f>I44*'Read me'!$B$4</f>
-        <v>45.6919</v>
+        <v>5.6571</v>
       </c>
       <c r="L44" s="6">
         <f>F44*K44</f>
-        <v>182.7675</v>
+        <v>56.5709</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget hold</t>
+          <t xml:space="preserve">Buy now</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4380,17 +4380,17 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NextFPV (regular price; sale USD 128; backordered)</t>
+          <t xml:space="preserve">APC Propellers (price list PROP-PRICE-LIST_202602)</t>
         </is>
       </c>
       <c r="P44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nextfpv.com/products/tattu-r-line-4500mah-95c-6s1p-lipo-battery-pack-with-xt90s-plug-for-uav</t>
+          <t xml:space="preserve">https://www.apcprop.com/wp-content/uploads/2026/02/PROP-PRICE-LIST_202602.xlsx</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -4400,24 +4400,24 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.3, §4.2.3</t>
+          <t xml:space="preserve">§3.2.1, TC-06</t>
         </is>
       </c>
       <c r="U44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Label must show chemistry, capacity, voltage and C-rating. Keep the original packaging (§4.2.3). Lithium packs ship as dangerous goods: buy locally if possible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="57" customHeight="1">
+          <t xml:space="preserve">Commercial propellers only; tips may be clipped (§3.2.1). APC limit for E props: 150,000 / D(in) rpm, 7,500 rpm at 20 in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="43.5" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B11</t>
+          <t xml:space="preserve">B09b</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4432,19 +4432,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiPo charging sacks</t>
+          <t xml:space="preserve">Propellers: 21x13E (bench sweep)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commercial, unaltered, manufacturer-labelled; sized for the packs. Every battery (propulsion, receiver, sensor) is stored and charged in one.</t>
+          <t xml:space="preserve">APC 21x13E Thin Electric.</t>
         </is>
       </c>
       <c r="F45" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G45" s="15">
-        <v>11.98</v>
+        <v>21.09</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -4453,19 +4453,19 @@
       </c>
       <c r="I45" s="5">
         <f>G45</f>
-        <v>11.98</v>
+        <v>21.09</v>
       </c>
       <c r="J45" s="5">
         <f>F45*I45</f>
-        <v>71.88</v>
+        <v>42.18</v>
       </c>
       <c r="K45" s="6">
         <f>I45*'Read me'!$B$4</f>
-        <v>3.7237</v>
+        <v>6.5554</v>
       </c>
       <c r="L45" s="6">
         <f>F45*K45</f>
-        <v>22.3424</v>
+        <v>13.1108</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4479,22 +4479,22 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Racers Edge (HobbyEtc)</t>
+          <t xml:space="preserve">APC Propellers (price list PROP-PRICE-LIST_202602)</t>
         </is>
       </c>
       <c r="P45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://store.hobbyetc.com/parts/view/132874</t>
+          <t xml:space="preserve">https://www.apcprop.com/wp-content/uploads/2026/02/PROP-PRICE-LIST_202602.xlsx</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search result</t>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -4504,19 +4504,19 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.3</t>
+          <t xml:space="preserve">§3.2.1, TC-06</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="43.5" customHeight="1">
+          <t xml:space="preserve">Commercial propellers only (§3.2.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="70.5" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B12</t>
+          <t xml:space="preserve">B10</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -4531,19 +4531,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balance charger</t>
+          <t xml:space="preserve">Propulsion pack, 8S bench candidate</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AC/DC, 1–6S LiPo and LiFe. Reference: ToolkitRC M7AC (retailers disagree on its power rating; check). Skip if the lab has one.</t>
+          <t xml:space="preserve">Thunder Power RC TP3300-8SE55: 8S 3300 mAh, Elite 55C, 97.7 Wh; 674 g (maker's estimate). Price without connector.</t>
         </is>
       </c>
       <c r="F46" s="4">
         <v>1</v>
       </c>
       <c r="G46" s="15">
-        <v>96.99</v>
+        <v>151.99</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
@@ -4552,19 +4552,19 @@
       </c>
       <c r="I46" s="5">
         <f>G46</f>
-        <v>96.99</v>
+        <v>151.99</v>
       </c>
       <c r="J46" s="5">
         <f>F46*I46</f>
-        <v>96.99</v>
+        <v>151.99</v>
       </c>
       <c r="K46" s="6">
         <f>I46*'Read me'!$B$4</f>
-        <v>30.1473</v>
+        <v>47.2429</v>
       </c>
       <c r="L46" s="6">
         <f>F46*K46</f>
-        <v>30.1473</v>
+        <v>47.2429</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4578,22 +4578,22 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pyrodrone</t>
+          <t xml:space="preserve">Thunder Power RC</t>
         </is>
       </c>
       <c r="P46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pyrodrone.com/collections/chargers-1/brand_toolkitrc</t>
+          <t xml:space="preserve">https://www.thunderpowerrc.com/products/tp3300-8se55</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search result</t>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -4603,19 +4603,19 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Battery care</t>
+          <t xml:space="preserve">§3.2.3, §4.2.3, TC-06</t>
         </is>
       </c>
       <c r="U46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="43.5" customHeight="1">
+          <t xml:space="preserve">Label must show chemistry, capacity, voltage and C-rating. Keep the original packaging (§4.2.3). Lithium packs ship as dangerous goods: buy locally if possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="70.5" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B13</t>
+          <t xml:space="preserve">B10b</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4630,19 +4630,19 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAXI blade fuses</t>
+          <t xml:space="preserve">Propulsion pack, 12S bench candidate</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assortment: 40, 50, 60 and 80 A (Littelfuse MAXI 299 series) and 100 A (Littelfuse 0MAX100, purple).</t>
+          <t xml:space="preserve">MaxAmps LiPo 2000 12S 44.4 V: 88.8 Wh; maximum continuous 54 A, so its fuse is capped at 54 A (§3.2.3.2); 586 g.</t>
         </is>
       </c>
       <c r="F47" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G47" s="15">
-        <v>3.0</v>
+        <v>372.0</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -4651,19 +4651,19 @@
       </c>
       <c r="I47" s="5">
         <f>G47</f>
-        <v>3.0</v>
+        <v>372.0</v>
       </c>
       <c r="J47" s="5">
         <f>F47*I47</f>
-        <v>45.0</v>
+        <v>372.0</v>
       </c>
       <c r="K47" s="6">
         <f>I47*'Read me'!$B$4</f>
-        <v>0.9325</v>
+        <v>115.6284</v>
       </c>
       <c r="L47" s="6">
         <f>F47*K47</f>
-        <v>13.9873</v>
+        <v>115.6284</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4672,22 +4672,27 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimate</t>
+          <t xml:space="preserve">Listing</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MaxAmps</t>
+        </is>
+      </c>
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://maxamps.com/products/lipo-2000-12s-44-4v-battery-pack</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -4697,19 +4702,19 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.3.1, §3.2.3.2</t>
+          <t xml:space="preserve">§3.2.3, §4.2.3, TC-06</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuse rating ≤ the pack's maximum continuous current, capped at 100 A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="57" customHeight="1">
+          <t xml:space="preserve">Label must show chemistry, capacity, voltage and C-rating. Keep the original packaging (§4.2.3). Lithium packs ship as dangerous goods: buy locally if possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="70.5" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B14</t>
+          <t xml:space="preserve">B10c</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -4724,19 +4729,19 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inline MAXI fuse holders</t>
+          <t xml:space="preserve">Propulsion packs, flight set (after D9)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rated at least as high as the fuse; for 10–12 AWG. Reference: GEP waterproof MAXI kit (up to 100 A, 12–10 AWG terminals, fuse not included).</t>
+          <t xml:space="preserve">Four packs of the system chosen at D9: TP3300-8SE55 (US$151.99) or MaxAmps 12S 2000 (US$372.00). Held at the higher price.</t>
         </is>
       </c>
       <c r="F48" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G48" s="15">
-        <v>16.95</v>
+        <v>372.0</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
@@ -4745,23 +4750,23 @@
       </c>
       <c r="I48" s="5">
         <f>G48</f>
-        <v>16.95</v>
+        <v>372.0</v>
       </c>
       <c r="J48" s="5">
         <f>F48*I48</f>
-        <v>101.7</v>
+        <v>1488.0</v>
       </c>
       <c r="K48" s="6">
         <f>I48*'Read me'!$B$4</f>
-        <v>5.2686</v>
+        <v>115.6284</v>
       </c>
       <c r="L48" s="6">
         <f>F48*K48</f>
-        <v>31.6113</v>
+        <v>462.5136</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buy now</t>
+          <t xml:space="preserve">Budget hold</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4771,44 +4776,44 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CE Auto Electric Supply</t>
+          <t xml:space="preserve">MaxAmps</t>
         </is>
       </c>
       <c r="P48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://ceautoelectricsupply.com/product/gep-waterproof-maxi-fuse-holder-kit/</t>
+          <t xml:space="preserve">https://maxamps.com/products/lipo-2000-12s-44-4v-battery-pack</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search result</t>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.3.1</t>
+          <t xml:space="preserve">§3.2.3, §4.2.3, DB-01 D9</t>
         </is>
       </c>
       <c r="U48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">One fuse harness per propulsion pack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="43.5" customHeight="1">
+          <t xml:space="preserve">Label must show chemistry, capacity, voltage and C-rating. Keep the original packaging (§4.2.3). Lithium packs ship as dangerous goods: buy locally if possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="57" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B15</t>
+          <t xml:space="preserve">B11</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4823,19 +4828,19 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arming-plug connectors</t>
+          <t xml:space="preserve">LiPo charging sacks</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">XT90-S anti-spark pairs (or the packs' connector) and XT90E-M panel mounts.</t>
+          <t xml:space="preserve">Commercial, unaltered, manufacturer-labelled; sized for the packs. Every battery (propulsion, receiver, sensor) is stored and charged in one.</t>
         </is>
       </c>
       <c r="F49" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G49" s="15">
-        <v>2.5</v>
+        <v>11.98</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -4844,19 +4849,19 @@
       </c>
       <c r="I49" s="5">
         <f>G49</f>
-        <v>2.5</v>
+        <v>11.98</v>
       </c>
       <c r="J49" s="5">
         <f>F49*I49</f>
-        <v>25.0</v>
+        <v>71.88</v>
       </c>
       <c r="K49" s="6">
         <f>I49*'Read me'!$B$4</f>
-        <v>0.7771</v>
+        <v>3.7237</v>
       </c>
       <c r="L49" s="6">
         <f>F49*K49</f>
-        <v>7.7707</v>
+        <v>22.3424</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -4865,12 +4870,17 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimate</t>
+          <t xml:space="preserve">Listing</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Racers Edge (HobbyEtc)</t>
+        </is>
+      </c>
+      <c r="P49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://store.hobbyetc.com/parts/view/132874</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -4880,7 +4890,7 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Search result</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -4890,19 +4900,19 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.2</t>
+          <t xml:space="preserve">§3.2.3</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arming-plug wire must be the same gauge as the pack leads or heavier (10 AWG on the reference pack).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="57" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B16</t>
+          <t xml:space="preserve">B12</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -4917,19 +4927,19 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silicone wire</t>
+          <t xml:space="preserve">Balance charger, 1–12S</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 AWG and 12 AWG, red and black, 3 m of each.</t>
+          <t xml:space="preserve">iCharger X12: up to 12S, 0.1–30 A, 1100 W charge power, 2 A balancing, DC input 11–53 V (needs B12b). Balance leads or adapters for the 8S and 12S packs are separate.</t>
         </is>
       </c>
       <c r="F50" s="4">
         <v>1</v>
       </c>
       <c r="G50" s="15">
-        <v>30.0</v>
+        <v>179.99</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
@@ -4938,19 +4948,19 @@
       </c>
       <c r="I50" s="5">
         <f>G50</f>
-        <v>30.0</v>
+        <v>179.99</v>
       </c>
       <c r="J50" s="5">
         <f>F50*I50</f>
-        <v>30.0</v>
+        <v>179.99</v>
       </c>
       <c r="K50" s="6">
         <f>I50*'Read me'!$B$4</f>
-        <v>9.3249</v>
+        <v>55.9461</v>
       </c>
       <c r="L50" s="6">
         <f>F50*K50</f>
-        <v>9.3249</v>
+        <v>55.9461</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -4959,22 +4969,27 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimate</t>
+          <t xml:space="preserve">Listing</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ProgressiveRC (iCharger US distributor)</t>
+        </is>
+      </c>
+      <c r="P50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://progressiverc.com/products/icharger-x12</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -4984,19 +4999,19 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.2</t>
+          <t xml:space="preserve">Battery care, TC-06</t>
         </is>
       </c>
       <c r="U50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
+          <t xml:space="preserve">Replaces the 1–6S charger of 9 Oct, which cannot charge either candidate pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="43.5" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B17</t>
+          <t xml:space="preserve">B12b</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -5011,19 +5026,19 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Watt meter</t>
+          <t xml:space="preserve">Charger power supply, 48 V</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ToolkitRC WM150, 1–50 V, 150 A.</t>
+          <t xml:space="preserve">Mean Well RSP-1000-48: 48 V DC, 21 A, 1008 W, AC input 90–264 V. Powers B12 at full power.</t>
         </is>
       </c>
       <c r="F51" s="4">
         <v>1</v>
       </c>
       <c r="G51" s="15">
-        <v>51.99</v>
+        <v>298.21</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -5032,19 +5047,19 @@
       </c>
       <c r="I51" s="5">
         <f>G51</f>
-        <v>51.99</v>
+        <v>298.21</v>
       </c>
       <c r="J51" s="5">
         <f>F51*I51</f>
-        <v>51.99</v>
+        <v>298.21</v>
       </c>
       <c r="K51" s="6">
         <f>I51*'Read me'!$B$4</f>
-        <v>16.16</v>
+        <v>92.6923</v>
       </c>
       <c r="L51" s="6">
         <f>F51*K51</f>
-        <v>16.16</v>
+        <v>92.6923</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -5058,22 +5073,22 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pyrodrone</t>
+          <t xml:space="preserve">TRC Electronics (Mean Well distributor; tariff included)</t>
         </is>
       </c>
       <c r="P51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pyrodrone.com/products/toolkitrc-wm150-advanced-watt-power-meter</t>
+          <t xml:space="preserve">https://www.trcelectronics.com/View/Mean-Well/RSP-1000-48.shtml</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search result</t>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -5083,19 +5098,19 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thrust and energy tests</t>
+          <t xml:space="preserve">Battery care, TC-06</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
+          <t xml:space="preserve">Enclosed unit with screw terminals: the AC side must be wired by someone qualified, with an earth connection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="138" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B18</t>
+          <t xml:space="preserve">B13</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -5110,19 +5125,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thrust-stand parts</t>
+          <t xml:space="preserve">MAXI blade fuses</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load cell (≥ 5 kg), HX711 amplifier, frame stock.</t>
+          <t xml:space="preserve">Assortment of MAXI blade fuses (rules Figure 5 shows a 100 A MAXI): 40, 50, 60, 80 and 100 A. Voltage rating to be confirmed before ordering: see notes.</t>
         </is>
       </c>
       <c r="F52" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G52" s="15">
-        <v>40.0</v>
+        <v>3.0</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
@@ -5131,19 +5146,19 @@
       </c>
       <c r="I52" s="5">
         <f>G52</f>
-        <v>40.0</v>
+        <v>3.0</v>
       </c>
       <c r="J52" s="5">
         <f>F52*I52</f>
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="K52" s="6">
         <f>I52*'Read me'!$B$4</f>
-        <v>12.4332</v>
+        <v>0.9325</v>
       </c>
       <c r="L52" s="6">
         <f>F52*K52</f>
-        <v>12.4332</v>
+        <v>13.9873</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -5177,19 +5192,19 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thrust test (proposal Table 10)</t>
+          <t xml:space="preserve">§3.2.3.1, §3.2.3.2</t>
         </is>
       </c>
       <c r="U52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
+          <t xml:space="preserve">Fuse rating ≤ the pack's maximum continuous current, capped at 100 A (§3.2.3.2); the 12S candidate pack is rated 54 A. UNVERIFIED (16 Oct): search results say the 100 A MAXI is a 32 V part and Littelfuse's 58 V MAXI series stops at 80 A; 8S is 33.6 V and 12S is 50.4 V when full. littelfuse.com blocks scripted reads: check the Littelfuse pages in a browser before ordering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="57" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B19</t>
+          <t xml:space="preserve">B14</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -5199,24 +5214,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Airframe and hardware</t>
+          <t xml:space="preserve">Propulsion and power</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV digital servos</t>
+          <t xml:space="preserve">Inline MAXI fuse holders</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.0–8.4 V, metal gear; size and torque from sizing.</t>
+          <t xml:space="preserve">Rated at least as high as the fuse; for 10–12 AWG. Reference: GEP waterproof MAXI kit (up to 100 A, 12–10 AWG terminals, fuse not included).</t>
         </is>
       </c>
       <c r="F53" s="4">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G53" s="15">
-        <v>45.0</v>
+        <v>16.95</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -5225,33 +5240,38 @@
       </c>
       <c r="I53" s="5">
         <f>G53</f>
-        <v>45.0</v>
+        <v>16.95</v>
       </c>
       <c r="J53" s="5">
         <f>F53*I53</f>
-        <v>720.0</v>
+        <v>101.7</v>
       </c>
       <c r="K53" s="6">
         <f>I53*'Read me'!$B$4</f>
-        <v>13.9873</v>
+        <v>5.2686</v>
       </c>
       <c r="L53" s="6">
         <f>F53*K53</f>
-        <v>223.7969</v>
+        <v>31.6113</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget hold</t>
+          <t xml:space="preserve">Buy now</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimate</t>
+          <t xml:space="preserve">Listing</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CE Auto Electric Supply</t>
+        </is>
+      </c>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://ceautoelectricsupply.com/product/gep-waterproof-maxi-fuse-holder-kit/</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -5261,29 +5281,29 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Search result</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.1</t>
+          <t xml:space="preserve">§3.2.3.1</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV rating needed for the 2S LiFe receiver pack (7.2 V full).</t>
+          <t xml:space="preserve">One fuse harness per propulsion pack.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="43.5" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B20</t>
+          <t xml:space="preserve">B15</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -5293,24 +5313,24 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Airframe and hardware</t>
+          <t xml:space="preserve">Propulsion and power</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linkage hardware</t>
+          <t xml:space="preserve">Arming-plug connectors</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clevises with locking sleeves, commercial control horns, pushrods.</t>
+          <t xml:space="preserve">XT90-S anti-spark pairs (or the packs' connector) and XT90E-M panel mounts.</t>
         </is>
       </c>
       <c r="F54" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G54" s="15">
-        <v>40.0</v>
+        <v>2.5</v>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
@@ -5319,19 +5339,19 @@
       </c>
       <c r="I54" s="5">
         <f>G54</f>
-        <v>40.0</v>
+        <v>2.5</v>
       </c>
       <c r="J54" s="5">
         <f>F54*I54</f>
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="K54" s="6">
         <f>I54*'Read me'!$B$4</f>
-        <v>12.4332</v>
+        <v>0.7771</v>
       </c>
       <c r="L54" s="6">
         <f>F54*K54</f>
-        <v>12.4332</v>
+        <v>7.7707</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -5365,19 +5385,19 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.1, §4.2.1</t>
+          <t xml:space="preserve">§3.2.2</t>
         </is>
       </c>
       <c r="U54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clevises need a mechanical lock. Horns go on per the manufacturer's instructions, never glued to film alone.</t>
+          <t xml:space="preserve">Arming-plug wire must be the same gauge as the pack leads or heavier (10 AWG on the reference pack).</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B21</t>
+          <t xml:space="preserve">B16</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -5387,24 +5407,24 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Airframe and hardware</t>
+          <t xml:space="preserve">Propulsion and power</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fasteners and threadlocker</t>
+          <t xml:space="preserve">Silicone wire</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nylon-insert lock nuts, M2–M5 screws, washers, heat-set inserts, Loctite 243.</t>
+          <t xml:space="preserve">10 AWG and 12 AWG, red and black, 3 m of each.</t>
         </is>
       </c>
       <c r="F55" s="4">
         <v>1</v>
       </c>
       <c r="G55" s="15">
-        <v>60.0</v>
+        <v>30.0</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -5413,19 +5433,19 @@
       </c>
       <c r="I55" s="5">
         <f>G55</f>
-        <v>60.0</v>
+        <v>30.0</v>
       </c>
       <c r="J55" s="5">
         <f>F55*I55</f>
-        <v>60.0</v>
+        <v>30.0</v>
       </c>
       <c r="K55" s="6">
         <f>I55*'Read me'!$B$4</f>
-        <v>18.6497</v>
+        <v>9.3249</v>
       </c>
       <c r="L55" s="6">
         <f>F55*K55</f>
-        <v>18.6497</v>
+        <v>9.3249</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -5459,19 +5479,19 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.2.1, §4.2.1</t>
+          <t xml:space="preserve">§3.2.2</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every permanent fastener needs a secondary retention method.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="43.5" customHeight="1">
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70.5" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B22</t>
+          <t xml:space="preserve">B17</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -5481,24 +5501,24 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Airframe and hardware</t>
+          <t xml:space="preserve">Propulsion and power</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carbon-fibre tubes</t>
+          <t xml:space="preserve">Watt meter</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roll-wrapped; OD and wall from sizing (spar, tail boom). Reference: Rock West 45002, 3k twill, 0.983 × 1.055 × 72 in.</t>
+          <t xml:space="preserve">ToolkitRC WM150, 1–50 V, 150 A.</t>
         </is>
       </c>
       <c r="F56" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56" s="15">
-        <v>99.99</v>
+        <v>51.99</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
@@ -5507,23 +5527,23 @@
       </c>
       <c r="I56" s="5">
         <f>G56</f>
-        <v>99.99</v>
+        <v>51.99</v>
       </c>
       <c r="J56" s="5">
         <f>F56*I56</f>
-        <v>399.96</v>
+        <v>51.99</v>
       </c>
       <c r="K56" s="6">
         <f>I56*'Read me'!$B$4</f>
-        <v>31.0798</v>
+        <v>16.16</v>
       </c>
       <c r="L56" s="6">
         <f>F56*K56</f>
-        <v>124.3192</v>
+        <v>16.16</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget hold</t>
+          <t xml:space="preserve">Buy now</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -5533,12 +5553,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rock West Composites</t>
+          <t xml:space="preserve">Pyrodrone</t>
         </is>
       </c>
       <c r="P56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.rockwestcomposites.com/roll-wrapped-carbon-fiber-tubes</t>
+          <t xml:space="preserve">https://pyrodrone.com/products/toolkitrc-wm150-advanced-watt-power-meter</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -5548,29 +5568,29 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendor page</t>
+          <t xml:space="preserve">Search result</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sizing</t>
+          <t xml:space="preserve">Thrust and energy tests</t>
         </is>
       </c>
       <c r="U56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+          <t xml:space="preserve">Rated 1–50 V: a full 12S pack (50.4 V) exceeds it. On the bench the thrust stand (B18) measures voltage and current; keep this meter for 8S and field checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="97.5" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B23</t>
+          <t xml:space="preserve">B18</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -5580,24 +5600,24 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Airframe and hardware</t>
+          <t xml:space="preserve">Propulsion and power</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balsa and aircraft plywood</t>
+          <t xml:space="preserve">Thrust stand</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balsa sheet 1.5–6 mm; birch aircraft ply 1.5 and 3 mm.</t>
+          <t xml:space="preserve">Tyto Robotics Flight Stand 15: thrust 15 kgf, torque 8 N·m, 30,000 RPM, voltage 180 V, current 150 A (product page, 16 Oct 2026). Measures thrust, torque, RPM, voltage and current, which validating the motor maps and APC tables needs. Both candidates make about 10 kgf static and 3.4 N·m.</t>
         </is>
       </c>
       <c r="F57" s="4">
         <v>1</v>
       </c>
       <c r="G57" s="15">
-        <v>150.0</v>
+        <v>0.0</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -5606,19 +5626,19 @@
       </c>
       <c r="I57" s="5">
         <f>G57</f>
-        <v>150.0</v>
+        <v>0.0</v>
       </c>
       <c r="J57" s="5">
         <f>F57*I57</f>
-        <v>150.0</v>
+        <v>0.0</v>
       </c>
       <c r="K57" s="6">
         <f>I57*'Read me'!$B$4</f>
-        <v>46.6244</v>
+        <v>0.0</v>
       </c>
       <c r="L57" s="6">
         <f>F57*K57</f>
-        <v>46.6244</v>
+        <v>0.0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -5632,39 +5652,44 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tyto Robotics (price on quotation)</t>
+        </is>
+      </c>
+      <c r="P57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tytorobotics.com/pages/flight-stand-15</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sizing</t>
+          <t xml:space="preserve">TC-06, evidence E04, proposal Table 10</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">QUOTE NEEDED: Tyto publishes no price (its FAQ: quotation by configuration; sales@tytorobotics.com). US$0 here is not a price. The 9 Oct entry (5 kg load-cell kit) could not hold about 100 N. Tyto also sells WindShapers (open-jet fans) for thrust at airspeed.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B24</t>
+          <t xml:space="preserve">B19</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -5679,19 +5704,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foam boards</t>
+          <t xml:space="preserve">HV digital servos</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">XPS or EPS, 50 mm, for hot-wire wing cores.</t>
+          <t xml:space="preserve">6.0–8.4 V, metal gear; size and torque from sizing.</t>
         </is>
       </c>
       <c r="F58" s="4">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G58" s="15">
-        <v>15.0</v>
+        <v>45.0</v>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
@@ -5700,19 +5725,19 @@
       </c>
       <c r="I58" s="5">
         <f>G58</f>
-        <v>15.0</v>
+        <v>45.0</v>
       </c>
       <c r="J58" s="5">
         <f>F58*I58</f>
-        <v>90.0</v>
+        <v>720.0</v>
       </c>
       <c r="K58" s="6">
         <f>I58*'Read me'!$B$4</f>
-        <v>4.6624</v>
+        <v>13.9873</v>
       </c>
       <c r="L58" s="6">
         <f>F58*K58</f>
-        <v>27.9746</v>
+        <v>223.7969</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -5746,19 +5771,19 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sizing</t>
+          <t xml:space="preserve">§3.2.1</t>
         </is>
       </c>
       <c r="U58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
+          <t xml:space="preserve">HV rating needed for the 2S LiFe receiver pack (7.2 V full).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="43.5" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B25</t>
+          <t xml:space="preserve">B20</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -5773,19 +5798,19 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Covering</t>
+          <t xml:space="preserve">Linkage hardware</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat-shrink covering film or laminating film (the team has no composites capability).</t>
+          <t xml:space="preserve">Clevises with locking sleeves, commercial control horns, pushrods.</t>
         </is>
       </c>
       <c r="F59" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G59" s="15">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -5794,23 +5819,23 @@
       </c>
       <c r="I59" s="5">
         <f>G59</f>
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="J59" s="5">
         <f>F59*I59</f>
-        <v>120.0</v>
+        <v>40.0</v>
       </c>
       <c r="K59" s="6">
         <f>I59*'Read me'!$B$4</f>
-        <v>9.3249</v>
+        <v>12.4332</v>
       </c>
       <c r="L59" s="6">
         <f>F59*K59</f>
-        <v>37.2995</v>
+        <v>12.4332</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget hold</t>
+          <t xml:space="preserve">Buy now</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5835,24 +5860,24 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing plan</t>
+          <t xml:space="preserve">§3.2.1, §4.2.1</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Clevises need a mechanical lock. Horns go on per the manufacturer's instructions, never glued to film alone.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B26</t>
+          <t xml:space="preserve">B21</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -5867,16 +5892,16 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landing gear and wheels</t>
+          <t xml:space="preserve">Fasteners and threadlocker</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set by the gear trade (tricycle or taildragger).</t>
+          <t xml:space="preserve">Nylon-insert lock nuts, M2–M5 screws, washers, heat-set inserts, Loctite 243.</t>
         </is>
       </c>
       <c r="F60" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="15">
         <v>60.0</v>
@@ -5892,7 +5917,7 @@
       </c>
       <c r="J60" s="5">
         <f>F60*I60</f>
-        <v>120.0</v>
+        <v>60.0</v>
       </c>
       <c r="K60" s="6">
         <f>I60*'Read me'!$B$4</f>
@@ -5900,11 +5925,11 @@
       </c>
       <c r="L60" s="6">
         <f>F60*K60</f>
-        <v>37.2995</v>
+        <v>18.6497</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget hold</t>
+          <t xml:space="preserve">Buy now</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5929,24 +5954,24 @@
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuration trade</t>
+          <t xml:space="preserve">§3.2.1, §4.2.1</t>
         </is>
       </c>
       <c r="U60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Every permanent fastener needs a secondary retention method.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="43.5" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B27</t>
+          <t xml:space="preserve">B22</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -5961,19 +5986,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adhesives and shop consumables</t>
+          <t xml:space="preserve">Carbon-fibre tubes</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA (thin, medium, thick) and accelerator, 5- and 30-minute epoxy, hot glue, sandpaper, blades, zip ties, hook-and-loop, heat-shrink.</t>
+          <t xml:space="preserve">Roll-wrapped; OD and wall from sizing (spar, tail boom). Reference: Rock West 45002, 3k twill, 0.983 × 1.055 × 72 in.</t>
         </is>
       </c>
       <c r="F61" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G61" s="15">
-        <v>150.0</v>
+        <v>99.99</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -5982,33 +6007,38 @@
       </c>
       <c r="I61" s="5">
         <f>G61</f>
-        <v>150.0</v>
+        <v>99.99</v>
       </c>
       <c r="J61" s="5">
         <f>F61*I61</f>
-        <v>150.0</v>
+        <v>399.96</v>
       </c>
       <c r="K61" s="6">
         <f>I61*'Read me'!$B$4</f>
-        <v>46.6244</v>
+        <v>31.0798</v>
       </c>
       <c r="L61" s="6">
         <f>F61*K61</f>
-        <v>46.6244</v>
+        <v>124.3192</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buy now</t>
+          <t xml:space="preserve">Budget hold</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimate</t>
+          <t xml:space="preserve">Listing</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rock West Composites</t>
+        </is>
+      </c>
+      <c r="P61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.rockwestcomposites.com/roll-wrapped-carbon-fiber-tubes</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -6018,29 +6048,29 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Build</t>
+          <t xml:space="preserve">Sizing</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 2026 judges flagged missing consumables in the budget.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B28</t>
+          <t xml:space="preserve">B23</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -6050,24 +6080,24 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+          <t xml:space="preserve">Airframe and hardware</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slip rings</t>
+          <t xml:space="preserve">Balsa and aircraft plywood</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capsule slip ring, 22 mm flange, 6 wires, 2 A, up to 300 rpm (Adafruit 736).</t>
+          <t xml:space="preserve">Balsa sheet 1.5–6 mm; birch aircraft ply 1.5 and 3 mm.</t>
         </is>
       </c>
       <c r="F62" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" s="15">
-        <v>14.95</v>
+        <v>150.0</v>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
@@ -6076,38 +6106,33 @@
       </c>
       <c r="I62" s="5">
         <f>G62</f>
-        <v>14.95</v>
+        <v>150.0</v>
       </c>
       <c r="J62" s="5">
         <f>F62*I62</f>
-        <v>44.85</v>
+        <v>150.0</v>
       </c>
       <c r="K62" s="6">
         <f>I62*'Read me'!$B$4</f>
-        <v>4.6469</v>
+        <v>46.6244</v>
       </c>
       <c r="L62" s="6">
         <f>F62*K62</f>
-        <v>13.9407</v>
+        <v>46.6244</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buy now</t>
+          <t xml:space="preserve">Budget hold</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listing</t>
+          <t xml:space="preserve">Estimate</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adafruit</t>
-        </is>
-      </c>
-      <c r="P62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.adafruit.com/product/736</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -6117,17 +6142,17 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendor page</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SR-06, SR-07</t>
+          <t xml:space="preserve">Sizing</t>
         </is>
       </c>
       <c r="U62" s="7" t="inlineStr">
@@ -6139,7 +6164,7 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B29</t>
+          <t xml:space="preserve">B24</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -6149,24 +6174,24 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+          <t xml:space="preserve">Airframe and hardware</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel actuator candidates</t>
+          <t xml:space="preserve">Foam boards</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-turn sail-winch servo or DC gearmotor with encoder; torque and turns from Script 5.</t>
+          <t xml:space="preserve">XPS or EPS, 50 mm, for hot-wire wing cores.</t>
         </is>
       </c>
       <c r="F63" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G63" s="15">
-        <v>45.0</v>
+        <v>15.0</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -6175,19 +6200,19 @@
       </c>
       <c r="I63" s="5">
         <f>G63</f>
-        <v>45.0</v>
+        <v>15.0</v>
       </c>
       <c r="J63" s="5">
         <f>F63*I63</f>
-        <v>135.0</v>
+        <v>90.0</v>
       </c>
       <c r="K63" s="6">
         <f>I63*'Read me'!$B$4</f>
-        <v>13.9873</v>
+        <v>4.6624</v>
       </c>
       <c r="L63" s="6">
         <f>F63*K63</f>
-        <v>41.9619</v>
+        <v>27.9746</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -6221,7 +6246,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SR-06, Script 5</t>
+          <t xml:space="preserve">Sizing</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
@@ -6230,10 +6255,10 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="43.5" customHeight="1">
+    <row r="64" ht="30" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B30</t>
+          <t xml:space="preserve">B25</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6243,24 +6268,24 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+          <t xml:space="preserve">Airframe and hardware</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tow-line conductor</t>
+          <t xml:space="preserve">Covering</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-conductor 28–30 AWG PTFE or silicone wire, 10 m. Strength member: the PE braid (A11).</t>
+          <t xml:space="preserve">Heat-shrink covering film or laminating film (the team has no composites capability).</t>
         </is>
       </c>
       <c r="F64" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G64" s="15">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
@@ -6269,23 +6294,23 @@
       </c>
       <c r="I64" s="5">
         <f>G64</f>
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="J64" s="5">
         <f>F64*I64</f>
-        <v>24.0</v>
+        <v>120.0</v>
       </c>
       <c r="K64" s="6">
         <f>I64*'Read me'!$B$4</f>
-        <v>3.7299</v>
+        <v>9.3249</v>
       </c>
       <c r="L64" s="6">
         <f>F64*K64</f>
-        <v>7.4599</v>
+        <v>37.2995</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buy now</t>
+          <t xml:space="preserve">Budget hold</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -6310,24 +6335,24 @@
       </c>
       <c r="S64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SR-06, SR-07</t>
+          <t xml:space="preserve">Manufacturing plan</t>
         </is>
       </c>
       <c r="U64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The tow line carries both the mechanical and the electrical connection (§3.1.1).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B31</t>
+          <t xml:space="preserve">B26</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -6337,24 +6362,24 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+          <t xml:space="preserve">Airframe and hardware</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Locking micro connectors</t>
+          <t xml:space="preserve">Landing gear and wheels</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">JST-GH 2–4 pin with pre-crimped leads, for the tow-line electrical interface.</t>
+          <t xml:space="preserve">Set by the gear trade (tricycle or taildragger).</t>
         </is>
       </c>
       <c r="F65" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" s="15">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -6363,23 +6388,23 @@
       </c>
       <c r="I65" s="5">
         <f>G65</f>
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="J65" s="5">
         <f>F65*I65</f>
-        <v>20.0</v>
+        <v>120.0</v>
       </c>
       <c r="K65" s="6">
         <f>I65*'Read me'!$B$4</f>
-        <v>6.2166</v>
+        <v>18.6497</v>
       </c>
       <c r="L65" s="6">
         <f>F65*K65</f>
-        <v>6.2166</v>
+        <v>37.2995</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buy now</t>
+          <t xml:space="preserve">Budget hold</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -6404,12 +6429,12 @@
       </c>
       <c r="S65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SR-07</t>
+          <t xml:space="preserve">Configuration trade</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
@@ -6418,10 +6443,10 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
+    <row r="66" ht="43.5" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B32</t>
+          <t xml:space="preserve">B27</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6431,45 +6456,45 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+          <t xml:space="preserve">Airframe and hardware</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensor light-controller MCU</t>
+          <t xml:space="preserve">Adhesives and shop consumables</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seeed XIAO RP2040 (21 × 17.5 mm).</t>
+          <t xml:space="preserve">CA (thin, medium, thick) and accelerator, 5- and 30-minute epoxy, hot glue, sandpaper, blades, zip ties, hook-and-loop, heat-shrink.</t>
         </is>
       </c>
       <c r="F66" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G66" s="15">
-        <v>3.9</v>
+        <v>150.0</v>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBP</t>
+          <t xml:space="preserve">USD</t>
         </is>
       </c>
       <c r="I66" s="5">
-        <f>G66*'Read me'!$B$5</f>
-        <v>5.1593</v>
+        <f>G66</f>
+        <v>150.0</v>
       </c>
       <c r="J66" s="5">
         <f>F66*I66</f>
-        <v>20.6372</v>
+        <v>150.0</v>
       </c>
       <c r="K66" s="6">
         <f>I66*'Read me'!$B$4</f>
-        <v>1.6037</v>
+        <v>46.6244</v>
       </c>
       <c r="L66" s="6">
         <f>F66*K66</f>
-        <v>6.4147</v>
+        <v>46.6244</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
@@ -6478,17 +6503,12 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listing</t>
+          <t xml:space="preserve">Estimate</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Pi Hut (incl. VAT)</t>
-        </is>
-      </c>
-      <c r="P66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://thepihut.com/collections/all/products/seeed-xiao-rp2040</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6498,7 +6518,7 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search result</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
@@ -6508,19 +6528,19 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SR-07, §3.1.1</t>
+          <t xml:space="preserve">Build</t>
         </is>
       </c>
       <c r="U66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Describe it only as payload light control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="57" customHeight="1">
+          <t xml:space="preserve">The 2026 judges flagged missing consumables in the budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B33</t>
+          <t xml:space="preserve">B28</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -6535,19 +6555,19 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sensor test-box parts</t>
+          <t xml:space="preserve">Slip rings</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-position switch, mating tow-line connector, printed enclosure, battery holder. Generates the same 1000 / 1500 / 2000 µs PWM as the receiver channel.</t>
+          <t xml:space="preserve">Capsule slip ring, 22 mm flange, 6 wires, 2 A, up to 300 rpm (Adafruit 736).</t>
         </is>
       </c>
       <c r="F67" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="15">
-        <v>20.0</v>
+        <v>14.95</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
@@ -6556,19 +6576,19 @@
       </c>
       <c r="I67" s="5">
         <f>G67</f>
-        <v>20.0</v>
+        <v>14.95</v>
       </c>
       <c r="J67" s="5">
         <f>F67*I67</f>
-        <v>40.0</v>
+        <v>44.85</v>
       </c>
       <c r="K67" s="6">
         <f>I67*'Read me'!$B$4</f>
-        <v>6.2166</v>
+        <v>4.6469</v>
       </c>
       <c r="L67" s="6">
         <f>F67*K67</f>
-        <v>12.4332</v>
+        <v>13.9407</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -6577,12 +6597,17 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimate</t>
+          <t xml:space="preserve">Listing</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Adafruit</t>
+        </is>
+      </c>
+      <c r="P67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.adafruit.com/product/736</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -6592,7 +6617,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Vendor page</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -6602,19 +6627,19 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">§3.1.1, §3.3.4, §4.1</t>
+          <t xml:space="preserve">SR-06, SR-07</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mandatory at tech inspection and in the Ground Mission.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B34</t>
+          <t xml:space="preserve">B29</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6629,19 +6654,19 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final sensor LEDs and batteries</t>
+          <t xml:space="preserve">Reel actuator candidates</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chosen from the TC-03 results.</t>
+          <t xml:space="preserve">Multi-turn sail-winch servo or DC gearmotor with encoder; torque and turns from Script 5.</t>
         </is>
       </c>
       <c r="F68" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68" s="15">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
@@ -6650,19 +6675,19 @@
       </c>
       <c r="I68" s="5">
         <f>G68</f>
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="J68" s="5">
         <f>F68*I68</f>
-        <v>40.0</v>
+        <v>135.0</v>
       </c>
       <c r="K68" s="6">
         <f>I68*'Read me'!$B$4</f>
-        <v>12.4332</v>
+        <v>13.9873</v>
       </c>
       <c r="L68" s="6">
         <f>F68*K68</f>
-        <v>12.4332</v>
+        <v>41.9619</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -6696,7 +6721,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-03</t>
+          <t xml:space="preserve">SR-06, Script 5</t>
         </is>
       </c>
       <c r="U68" s="7" t="inlineStr">
@@ -6705,10 +6730,10 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
+    <row r="69" ht="43.5" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B35</t>
+          <t xml:space="preserve">B30</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -6718,24 +6743,24 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logistics</t>
+          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping crate materials</t>
+          <t xml:space="preserve">Tow-line conductor</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plywood, foam and hardware for a travel crate.</t>
+          <t xml:space="preserve">2-conductor 28–30 AWG PTFE or silicone wire, 10 m. Strength member: the PE braid (A11).</t>
         </is>
       </c>
       <c r="F69" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="15">
-        <v>150.0</v>
+        <v>12.0</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
@@ -6744,134 +6769,609 @@
       </c>
       <c r="I69" s="5">
         <f>G69</f>
-        <v>150.0</v>
+        <v>12.0</v>
       </c>
       <c r="J69" s="5">
         <f>F69*I69</f>
-        <v>150.0</v>
+        <v>24.0</v>
       </c>
       <c r="K69" s="6">
         <f>I69*'Read me'!$B$4</f>
-        <v>46.6244</v>
+        <v>3.7299</v>
       </c>
       <c r="L69" s="6">
         <f>F69*K69</f>
+        <v>7.4599</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buy now</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimate</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-01</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SR-06, SR-07</t>
+        </is>
+      </c>
+      <c r="U69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tow line carries both the mechanical and the electrical connection (§3.1.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B31</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locking micro connectors</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JST-GH 2–4 pin with pre-crimped leads, for the tow-line electrical interface.</t>
+        </is>
+      </c>
+      <c r="F70" s="4">
+        <v>1</v>
+      </c>
+      <c r="G70" s="15">
+        <v>20.0</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="I70" s="5">
+        <f>G70</f>
+        <v>20.0</v>
+      </c>
+      <c r="J70" s="5">
+        <f>F70*I70</f>
+        <v>20.0</v>
+      </c>
+      <c r="K70" s="6">
+        <f>I70*'Read me'!$B$4</f>
+        <v>6.2166</v>
+      </c>
+      <c r="L70" s="6">
+        <f>F70*K70</f>
+        <v>6.2166</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buy now</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimate</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-01</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SR-07</t>
+        </is>
+      </c>
+      <c r="U70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B32</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensor light-controller MCU</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seeed XIAO RP2040 (21 × 17.5 mm).</t>
+        </is>
+      </c>
+      <c r="F71" s="4">
+        <v>4</v>
+      </c>
+      <c r="G71" s="15">
+        <v>3.9</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GBP</t>
+        </is>
+      </c>
+      <c r="I71" s="5">
+        <f>G71*'Read me'!$B$5</f>
+        <v>5.1593</v>
+      </c>
+      <c r="J71" s="5">
+        <f>F71*I71</f>
+        <v>20.6372</v>
+      </c>
+      <c r="K71" s="6">
+        <f>I71*'Read me'!$B$4</f>
+        <v>1.6037</v>
+      </c>
+      <c r="L71" s="6">
+        <f>F71*K71</f>
+        <v>6.4147</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buy now</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listing</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Pi Hut (incl. VAT)</t>
+        </is>
+      </c>
+      <c r="P71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thepihut.com/collections/all/products/seeed-xiao-rp2040</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Search result</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-01</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SR-07, §3.1.1</t>
+        </is>
+      </c>
+      <c r="U71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Describe it only as payload light control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="57" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B33</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensor test-box parts</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3-position switch, mating tow-line connector, printed enclosure, battery holder. Generates the same 1000 / 1500 / 2000 µs PWM as the receiver channel.</t>
+        </is>
+      </c>
+      <c r="F72" s="4">
+        <v>2</v>
+      </c>
+      <c r="G72" s="15">
+        <v>20.0</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="I72" s="5">
+        <f>G72</f>
+        <v>20.0</v>
+      </c>
+      <c r="J72" s="5">
+        <f>F72*I72</f>
+        <v>40.0</v>
+      </c>
+      <c r="K72" s="6">
+        <f>I72*'Read me'!$B$4</f>
+        <v>6.2166</v>
+      </c>
+      <c r="L72" s="6">
+        <f>F72*K72</f>
+        <v>12.4332</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buy now</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimate</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-01</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">§3.1.1, §3.3.4, §4.1</t>
+        </is>
+      </c>
+      <c r="U72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mandatory at tech inspection and in the Ground Mission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B34</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensor, D&amp;R and test box</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Final sensor LEDs and batteries</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chosen from the TC-03 results.</t>
+        </is>
+      </c>
+      <c r="F73" s="4">
+        <v>1</v>
+      </c>
+      <c r="G73" s="15">
+        <v>40.0</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="I73" s="5">
+        <f>G73</f>
+        <v>40.0</v>
+      </c>
+      <c r="J73" s="5">
+        <f>F73*I73</f>
+        <v>40.0</v>
+      </c>
+      <c r="K73" s="6">
+        <f>I73*'Read me'!$B$4</f>
+        <v>12.4332</v>
+      </c>
+      <c r="L73" s="6">
+        <f>F73*K73</f>
+        <v>12.4332</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Budget hold</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimate</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-09</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-30</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03</t>
+        </is>
+      </c>
+      <c r="U73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B35</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logistics</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shipping crate materials</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plywood, foam and hardware for a travel crate.</t>
+        </is>
+      </c>
+      <c r="F74" s="4">
+        <v>1</v>
+      </c>
+      <c r="G74" s="15">
+        <v>150.0</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="I74" s="5">
+        <f>G74</f>
+        <v>150.0</v>
+      </c>
+      <c r="J74" s="5">
+        <f>F74*I74</f>
+        <v>150.0</v>
+      </c>
+      <c r="K74" s="6">
+        <f>I74*'Read me'!$B$4</f>
         <v>46.6244</v>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="L74" s="6">
+        <f>F74*K74</f>
+        <v>46.6244</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Budget hold</t>
         </is>
       </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Estimate</t>
         </is>
       </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S69" s="3" t="inlineStr">
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
-      <c r="T69" s="2" t="inlineStr">
+      <c r="T74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Travel</t>
         </is>
       </c>
-      <c r="U69" s="7" t="inlineStr">
+      <c r="U74" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 judges flagged missing crating in the budget.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="I71" s="9" t="inlineStr">
+    <row r="76">
+      <c r="I76" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Tier A, local purchase</t>
         </is>
       </c>
-      <c r="J71" s="10">
-        <f>SUMIFS($J$2:$J$69,$B$2:$B$69,"A")</f>
+      <c r="J76" s="10">
+        <f>SUMIFS($J$2:$J$74,$B$2:$B$74,"A")</f>
         <v>1280.2</v>
       </c>
-      <c r="L71" s="11">
-        <f>J71*'Read me'!$B$4</f>
+      <c r="L76" s="11">
+        <f>J76*'Read me'!$B$4</f>
         <v>397.9233</v>
       </c>
     </row>
-    <row r="72">
-      <c r="I72" s="9" t="inlineStr">
+    <row r="77">
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Tier B, buy now</t>
         </is>
       </c>
-      <c r="J72" s="10">
-        <f>SUMIFS($J$2:$J$69,$B$2:$B$69,"B",$M$2:$M$69,"Buy now")</f>
-        <v>1315.9672</v>
-      </c>
-      <c r="L72" s="11">
-        <f>J72*'Read me'!$B$4</f>
-        <v>409.0408</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="I73" s="9" t="inlineStr">
+      <c r="J77" s="10">
+        <f>SUMIFS($J$2:$J$74,$B$2:$B$74,"B",$M$2:$M$74,"Buy now")</f>
+        <v>3713.1972</v>
+      </c>
+      <c r="L77" s="11">
+        <f>J77*'Read me'!$B$4</f>
+        <v>1154.1694</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="I78" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Tier B, budget holds</t>
         </is>
       </c>
-      <c r="J73" s="10">
-        <f>SUMIFS($J$2:$J$69,$B$2:$B$69,"B",$M$2:$M$69,"Budget hold")</f>
-        <v>3444.91</v>
-      </c>
-      <c r="L73" s="11">
-        <f>J73*'Read me'!$B$4</f>
-        <v>1070.7779</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="I74" s="9" t="inlineStr">
+      <c r="J78" s="10">
+        <f>SUMIFS($J$2:$J$74,$B$2:$B$74,"B",$M$2:$M$74,"Budget hold")</f>
+        <v>3850.96</v>
+      </c>
+      <c r="L78" s="11">
+        <f>J78*'Read me'!$B$4</f>
+        <v>1196.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="J74" s="10">
-        <f>SUM(J71:J73)</f>
-        <v>6041.0772</v>
-      </c>
-      <c r="L74" s="11">
-        <f>J74*'Read me'!$B$4</f>
-        <v>1877.742</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="I75" s="9" t="inlineStr">
+      <c r="J79" s="10">
+        <f>SUM(J76:J78)</f>
+        <v>8844.3572</v>
+      </c>
+      <c r="L79" s="11">
+        <f>J79*'Read me'!$B$4</f>
+        <v>2749.0827</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="I80" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Share backed by a listing</t>
         </is>
       </c>
-      <c r="J75" s="16">
-        <f>SUMIFS($J$2:$J$69,$N$2:$N$69,"Listing")/J74</f>
-        <v>0.522767</v>
+      <c r="J80" s="16">
+        <f>SUMIFS($J$2:$J$74,$N$2:$N$74,"Listing")/J79</f>
+        <v>0.678552</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U69"/>
+  <autoFilter ref="A1:U74"/>
   <hyperlinks>
     <hyperlink ref="P4" r:id="rIdL1"/>
     <hyperlink ref="P8" r:id="rIdL2"/>
@@ -6888,11 +7388,17 @@
     <hyperlink ref="P44" r:id="rIdL13"/>
     <hyperlink ref="P45" r:id="rIdL14"/>
     <hyperlink ref="P46" r:id="rIdL15"/>
-    <hyperlink ref="P48" r:id="rIdL16"/>
-    <hyperlink ref="P51" r:id="rIdL17"/>
-    <hyperlink ref="P56" r:id="rIdL18"/>
-    <hyperlink ref="P62" r:id="rIdL19"/>
-    <hyperlink ref="P66" r:id="rIdL20"/>
+    <hyperlink ref="P47" r:id="rIdL16"/>
+    <hyperlink ref="P48" r:id="rIdL17"/>
+    <hyperlink ref="P49" r:id="rIdL18"/>
+    <hyperlink ref="P50" r:id="rIdL19"/>
+    <hyperlink ref="P51" r:id="rIdL20"/>
+    <hyperlink ref="P53" r:id="rIdL21"/>
+    <hyperlink ref="P56" r:id="rIdL22"/>
+    <hyperlink ref="P57" r:id="rIdL23"/>
+    <hyperlink ref="P61" r:id="rIdL24"/>
+    <hyperlink ref="P67" r:id="rIdL25"/>
+    <hyperlink ref="P71" r:id="rIdL26"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/procurement/PR-01_initial_request.xlsx
+++ b/procurement/PR-01_initial_request.xlsx
@@ -7425,7 +7425,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">AIAA Design/Build/Fly 2026–27  ·  American University of the Middle East  ·  Doc AUM-DBF-27-PR-001  ·  Rev A  ·  9 Oct 2026</t>
+          <t xml:space="preserve">AIAA Design/Build/Fly 2026–27  ·  Badr Obtel  ·  Doc OBTEL-DBF-27-PR-001  ·  Rev A  ·  9 Oct 2026</t>
         </is>
       </c>
     </row>
